--- a/test-data/Sample_Venue.xlsx
+++ b/test-data/Sample_Venue.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">NewTown</t>
   </si>
   <si>
-    <t xml:space="preserve">Luton</t>
+    <t xml:space="preserve">Avon</t>
   </si>
   <si>
     <t xml:space="preserve">United Kingdom</t>
@@ -159,12 +159,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -423,81 +427,81 @@
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>1234456789</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>123456</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>18</v>
       </c>
     </row>
